--- a/InputData/trans/AVLo/cn - Avg Vehicle Loading.xlsx
+++ b/InputData/trans/AVLo/cn - Avg Vehicle Loading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPS-trans\伊皮埃斯\AVLo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\AVLo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F94FF1-65C7-4733-AEDB-084B55F9088B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA874A27-B606-40C7-A7A1-E57FA1DD3D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4469" yWindow="312" windowWidth="21709" windowHeight="13572" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2118,9 +2118,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2158,9 +2158,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2193,26 +2193,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2245,26 +2228,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2439,10 +2405,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" customWidth="1"/>
-    <col min="2" max="2" width="88.109375" customWidth="1"/>
+    <col min="1" max="1" width="11.5" customWidth="1"/>
+    <col min="2" max="2" width="88.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2593,12 +2559,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="50.44140625" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="131.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
+    <col min="1" max="1" width="50.5" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="131.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2656,7 +2622,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.6">
+    <row r="5" spans="1:8" ht="16.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2729,7 +2695,7 @@
         <v>52.197507357415731</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" thickBot="1">
+    <row r="12" spans="1:8" ht="13.6" thickBot="1">
       <c r="A12" s="12" t="s">
         <v>19</v>
       </c>
@@ -2765,7 +2731,7 @@
         <v>9052.3830236748909</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1">
+    <row r="17" spans="1:4" ht="13.6" thickBot="1">
       <c r="A17" s="17" t="s">
         <v>22</v>
       </c>
@@ -2810,7 +2776,7 @@
         <v>22909.960852544584</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1">
+    <row r="22" spans="1:4" ht="13.6" thickBot="1">
       <c r="A22" s="12" t="s">
         <v>25</v>
       </c>
@@ -2856,7 +2822,7 @@
         <v>182.43</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15" thickBot="1">
+    <row r="28" spans="1:4" ht="13.6" thickBot="1">
       <c r="A28" s="12" t="s">
         <v>25</v>
       </c>
@@ -2967,7 +2933,7 @@
         <v>0.90235358598174642</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15" thickBot="1">
+    <row r="39" spans="1:4" ht="13.6" thickBot="1">
       <c r="A39" s="17" t="s">
         <v>37</v>
       </c>
@@ -3026,7 +2992,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15" thickBot="1">
+    <row r="46" spans="1:4" ht="13.6" thickBot="1">
       <c r="A46" s="17" t="s">
         <v>40</v>
       </c>
@@ -3074,8 +3040,8 @@
     </row>
     <row r="53" spans="1:3">
       <c r="B53" s="37">
-        <f>B50*C36+B51*C37+B52*C38</f>
-        <v>17.533087393027898</v>
+        <f>(B50*C36+B51*C37+B52*C38)*2.34420989412966</f>
+        <v>41.101236941376001</v>
       </c>
       <c r="C53">
         <v>8158</v>
@@ -3136,12 +3102,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D106B0-C4F0-420C-81FE-F67A0635B1D7}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="86.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3331,7 +3297,7 @@
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
     </row>
-    <row r="15" spans="1:10" ht="100.8">
+    <row r="15" spans="1:10" ht="77.45">
       <c r="A15" s="29" t="s">
         <v>87</v>
       </c>
@@ -3500,9 +3466,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="36.44140625" customWidth="1"/>
+    <col min="1" max="1" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3537,7 +3503,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1">
+    <row r="4" spans="1:5" ht="13.6" thickBot="1">
       <c r="A4" s="12" t="s">
         <v>52</v>
       </c>
@@ -3562,7 +3528,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1">
+    <row r="7" spans="1:5" ht="13.6" thickBot="1">
       <c r="A7" s="12" t="s">
         <v>54</v>
       </c>
@@ -3600,9 +3566,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:AI7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="62.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="62.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:35">
@@ -3848,11 +3814,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C887045F-E524-44EF-90AC-4C1C5356BF2B}">
   <dimension ref="B1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
-    <col min="4" max="4" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="4" max="4" width="30.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4">
@@ -3894,10 +3860,10 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AS7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="13.109375" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.125" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45">
@@ -4763,179 +4729,179 @@
       </c>
       <c r="B6" s="23">
         <f>AVL!B53</f>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="C6" s="21">
         <f>B6</f>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="D6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="E6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="F6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="G6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="H6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="I6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="J6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="K6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="L6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="M6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="N6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="O6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="P6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="Q6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="R6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="S6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="T6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="U6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="V6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="W6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="X6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="Y6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="Z6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AA6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AB6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AC6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AD6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AE6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AF6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AG6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AH6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AI6" s="21">
         <f t="shared" si="13"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AJ6" s="21">
         <f t="shared" si="14"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" si="15"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AL6" s="21">
         <f t="shared" si="16"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AM6" s="21">
         <f t="shared" si="17"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AN6" s="21">
         <f t="shared" si="18"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AO6" s="21">
         <f t="shared" si="19"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AP6" s="21">
         <f t="shared" si="20"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AQ6" s="21">
         <f t="shared" si="21"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AR6" s="21">
         <f t="shared" si="22"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
       <c r="AS6" s="21">
         <f t="shared" si="23"/>
-        <v>17.533087393027898</v>
+        <v>41.101236941376001</v>
       </c>
     </row>
     <row r="7" spans="1:45">
@@ -5137,10 +5103,10 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AT7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
     <col min="3" max="36" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5286,184 +5252,183 @@
         <v>41</v>
       </c>
       <c r="B2" s="39">
-        <f>1.2*0.95</f>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="C2">
         <f t="shared" ref="C2:R2" si="0">$B2</f>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="D2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="E2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
         <f t="shared" ref="S2:AT2" si="1">$B2</f>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="U2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="V2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="X2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Y2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AA2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AB2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AC2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AD2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AF2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AG2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AH2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AI2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AJ2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AM2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AN2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AO2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AP2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AQ2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AR2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AS2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="AT2">
         <f t="shared" si="1"/>
-        <v>1.1399999999999999</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="3" spans="1:46">
@@ -5471,184 +5436,183 @@
         <v>42</v>
       </c>
       <c r="B3" s="30">
-        <f>11.4*0.95</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="C3" s="30">
         <f>B3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="D3" s="30">
         <f t="shared" ref="D3" si="2">C3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="E3" s="30">
         <f>D3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:AI3" si="3">E3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="G3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="H3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="I3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="J3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="K3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="L3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="M3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="N3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="O3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="P3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="Q3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="R3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="S3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="T3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="U3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="V3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="W3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="X3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="Y3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="Z3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AA3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AB3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AC3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AD3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AE3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AF3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AG3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AH3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AI3" s="30">
         <f t="shared" si="3"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AJ3" s="30">
         <f t="shared" ref="AJ3" si="4">AI3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AK3" s="30">
         <f t="shared" ref="AK3" si="5">AJ3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AL3" s="30">
         <f t="shared" ref="AL3" si="6">AK3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AM3" s="30">
         <f t="shared" ref="AM3" si="7">AL3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AN3" s="30">
         <f t="shared" ref="AN3" si="8">AM3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AO3" s="30">
         <f t="shared" ref="AO3" si="9">AN3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AP3" s="30">
         <f t="shared" ref="AP3" si="10">AO3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AQ3" s="30">
         <f t="shared" ref="AQ3" si="11">AP3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AR3" s="30">
         <f t="shared" ref="AR3" si="12">AQ3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AS3" s="30">
         <f t="shared" ref="AS3:AT3" si="13">AR3</f>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="AT3" s="30">
         <f t="shared" si="13"/>
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="4" spans="1:46">
@@ -6404,24 +6368,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6655,7 +6601,45 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DFCCD47-582B-4AB1-BAAE-0543951F7960}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B451E45-EBA9-468F-B06C-0D6295BBD487}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -6673,30 +6657,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46EC1CF8-DA8F-4EA5-8572-70E1ECE08709}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DFCCD47-582B-4AB1-BAAE-0543951F7960}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
-    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>